--- a/Line/config.xlsx
+++ b/Line/config.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b1gi5m\Desktop\Line\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE069EBA-A74E-4F91-A142-F7609EBEF134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AF822F-879E-465F-8B0D-24D9C67ECE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personas" sheetId="1" r:id="rId1"/>
     <sheet name="questions" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="31">
   <si>
     <t>나이</t>
   </si>
@@ -68,27 +69,6 @@
     <t>선택지2칸수</t>
   </si>
   <si>
-    <t>어쩔 수 없이 1~2년 단위로 이사를 다녀야 한다면</t>
-  </si>
-  <si>
-    <t>해당함</t>
-  </si>
-  <si>
-    <t>해당 없음</t>
-  </si>
-  <si>
-    <t>4대 보험을 받지 못하는 일을 하고 있는 가정이라면</t>
-  </si>
-  <si>
-    <t>가족 형태 때문에 학교나 또래 집단에서 놀림이나 곤란한 일을 겪은 적이 있다면</t>
-  </si>
-  <si>
-    <t>매 학기 원하는 학원이나 방과후 활동을 자유롭게 선택할 수 있다면</t>
-  </si>
-  <si>
-    <t>가족 여행을 1년에 한 번 이상 갈 수 있다면</t>
-  </si>
-  <si>
     <t>※ 순서: 질문이 제시되는 순번(숫자) / 질문내용: 학생에게 보여줄 문장</t>
   </si>
   <si>
@@ -107,103 +87,42 @@
     <t>※ 행을 추가/삭제해서 질문 개수를 자유롭게 바꿀 수 있습니다.</t>
   </si>
   <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 두 분 모두 대형 병원의 의사로 일하신다. 나는 부모님 두 분과 함께 생활하고 있다. 신체적으로 전혀 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 대학교수로 일하고 계신다. 부모님 중 한 분이 미국인이라 나는 한국과 미국 국적을 모두 가진 이중국적자이며, 서구적인 외모를 가지고 있다. 부모님 두 분과 함께 살고 있으며, 신체적으로 아픈 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 부산에 거주하고 있다. 부모님은 도심에 건물을 여러 채 소유한 건물주이시다. 나는 부모님 두 분과 함께 살고 있으며, 특별히 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 큰 기업의 임원으로 재직 중이시다. 나는 부모님 두 분과 함께 생활하고 있다. 신체적으로는 아픈 곳 없이 아주 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 정부에서 일하는 외교관이시다. 나는 해외에서 태어나 이중국적을 가지고 있으며, 부모님 두 분과 함께 생활한다. 신체와 정신 모두 아픈 곳 없이 매우 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 부산에 거주하고 있다. 부모님은 중견기업을 운영하시는 사업가이시다. 나는 부모님 두 분과 함께 생활하고 있다. 신체적으로는 전혀 불편함 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 현재 국회의원으로 일하고 계신다. 나는 부모님 두 분과 함께 생활한다. 특별히 아픈 곳 없이 건강한 편이다.</t>
-  </si>
-  <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 대형 로펌에서 일하는 변호사이시다. 나는 부모님 두 분과 함께 살고 있다. 신체적으로는 불편한 곳 없이 아주 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 부산에 거주하고 있다. 부모님은 대학병원에서 의사로 일하고 계신다. 나는 부모님 두 분과 함께 살고 있다. 특별히 아픈 곳 없이 건강한 상태이다.</t>
-  </si>
-  <si>
-    <t>나는 서울에 거주하고 있다. 부모님은 IT 기업의 대표로 재직 중이시다. 나는 부모님 두 분과 함께 살고 있다. 신체적으로는 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 부모님 중 한 분은 초등학교 교사이고, 다른 한 분은 일반 회사에 다니시는 맞벌이 가정이다. 나는 부모님 두 분과 함께 살고 있으며, 신체적으로는 전혀 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 부모님은 동네에서 식당을 운영하는 자영업자이시다. 나는 부모님 두 분과 함께 생활하고 있다. 특별히 아픈 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 부모님 중 한 분이 타 지역에서 근무하는 공무원이시다. 나는 평일에는 어머니와 지내고, 주말에는 아버지까지 부모님 두 분과 함께 지낸다. 신체적으로는 전혀 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 어머니는 일본에서 오셨고 아버지는 한국인이시다. 어머니는 한국어를 유창하게 사용하신다. 아버지는 은행원으로 일하시며 나는 부모님 두 분과 함께 산다. 신체적으로는 전혀 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 부모님은 동네에서 카센터를 운영하고 계신다. 나는 부모님 두 분과 함께 생활하고 있다. 신체적으로는 아픈 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 부모님 중 한 분은 종합병원 간호사이고, 다른 한 분은 일반 회사원이다. 나는 부모님 두 분과 함께 생활하고 있다. 신체적으로는 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 부모님 중 한 분은 소방관이고 다른 한 분은 전업주부이시다. 나는 부모님 두 분과 함께 살고 있으며, 특별히 아픈 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 어머니는 동네에서 미용실을 운영하고 계신다. 나는 어머니와 단둘이 생활하고 있으며, 신체적으로 불편함 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 아버지는 중국에서 오셨고 어머니는 한국인이시다. 아버지는 일상적인 한국어 소통에 무리가 없다. 부모님은 두 분 다 지역 공장의 숙련 기술직으로 일하신다. 나는 부모님 두 분과 함께 산다. 신체적으로 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 부모님은 두 분 다 일반 직장인이시다. 나는 부모님 두 분과 함께 살고 있으며, 특별히 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 강원도의 하루에 시내버스가 단 두 번 운행하는 산골에 거주하고 있다. 부모님은 영세 농업에 종사하신다. 나는 부모님 두 분과 함께 살고 있으며, 신체적으로는 특별히 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 전남의 육지에서 여객선을 타고 4시간을 이동해야만 도착하는 섬에 거주하고 있다. 부모님은 소형 어선으로 영세 어업을 하신다. 나는 부모님 두 분과 함께 생활하며, 특별히 불편한 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 우리 집은 매달 지급되는 기초생활수급비로 생활한다. 나는 부모님 없이 할머니와 단둘이 살고 있으며, 생활비를 보태기 위해 주말마다 하루 8시간씩 아르바이트를 한다. 신체적으로는 특별히 아픈 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 부모님은 공장에서 단순 육체노동을 하신다. 나는 부모님 두 분과 함께 살고 있다. 신체적으로 두 다리를 쓸 수 없어 휠체어를 타야 하는 지체장애를 가지고 있다.</t>
-  </si>
-  <si>
-    <t>나는 전북의 뭍으로 가려면 배를 두 번이나 갈아타야 하는 섬에 거주하고 있다. 부모님은 양식장 일손으로 일하느라 밤늦게 오셔서 내가 매일 어린 동생을 돌봐야 한다. 부모님 두 분과 함께 살며 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 경기도에 거주하고 있다. 우리 가족은 아프리카에서 내전을 피해 온 난민으로 아직 한국의 정식 체류 허가를 받지 못했다. 우리 가족은 한국어를 거의 하지 못하며, 피부색은 짙은 편이다. 나는 부모님 두 분과 함께 살고 있으며, 신체적으로는 불편한 곳 없이 건강하다.</t>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>값</t>
+  </si>
+  <si>
+    <t>오프닝문장</t>
+  </si>
+  <si>
+    <t>나는 중학교에 재학 중인 {나이}살 {성별}학생이다.</t>
+  </si>
+  <si>
+    <t>※ 오프닝문장: 캐릭터 문장 맨 앞에 붙는 성별·나이 소개 문장입니다.</t>
+  </si>
+  <si>
+    <t>※ {나이}와 {성별} 자리에 각각 캐릭터의 나이와 학생이 입장 시 선택한 성별이 자동으로 들어갑니다.</t>
+  </si>
+  <si>
+    <t>※ 자유롭게 문구를 바꿔도 되고, {나이}/{성별} 토큰의 위치도 원하는 대로 옮길 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  예: "{성별}학생인 나는 {나이}살, 중학교 2학년이다."</t>
+  </si>
+  <si>
+    <t>※ {성별}은 "남" 또는 "여"로만 채워집니다 ("남학생"이 아님) — "학생" 등은 템플릿에 직접 적어주세요.</t>
+  </si>
+  <si>
+    <t>테스트</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 아버지는 건설 현장에서 일용직 노동을 하신다. 나는 아버지와 단둘이 살고 있으며, 부족한 생활비를 벌기 위해 방과 후마다 매일 3시간씩 아르바이트를 한다. 신체적으로는 특별히 아픈 곳 없이 건강하다.</t>
-  </si>
-  <si>
-    <t>나는 세종에 거주하고 있다. 부모님은 작은 식당에서 주방 보조로 일하신다. 나는 부모님 두 분과 함께 살고 있다. 소리가 전혀 들리지 않는 청각장애를 가지고 있다.</t>
-  </si>
-  <si>
-    <t>나는 경북의 버스를 타려면 비포장도로를 1시간 동안 걸어가야 하는 산골에 거주하고 있다. 부모님은 영세 농업을 하시며, 어머니가 동남아시아에서 오셔서 한국어 소통이 많이 서투르시다. 어머니의 영향으로 내 피부색도 어두운 편이다. 부모님 두 분과 함께 살며 건강하다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 대전에 거주하고 있다. 우리 집은 기초생활수급비로 생활한다. 부모님은 몸이 불편하여 정기적인 직업이 없으시다. 나는 부모님 두 분과 함께 살고 있으며, 생활비를 보태기 위해 토요일과 일요일마다 하루 5시간씩 아르바이트를 한다. 안경을 써도 칠판 글씨가 잘 보이지 않는 시각장애를 가지고 있다.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +153,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -260,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -268,6 +193,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -570,14 +496,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,311 +511,308 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
         <v>15</v>
       </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
         <v>15</v>
       </c>
-      <c r="B20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
         <v>15</v>
       </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
         <v>15</v>
       </c>
-      <c r="B22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
         <v>15</v>
       </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
         <v>15</v>
       </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
         <v>15</v>
       </c>
-      <c r="B25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
         <v>15</v>
       </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
         <v>15</v>
       </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
         <v>15</v>
       </c>
-      <c r="B28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
         <v>15</v>
       </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
         <v>15</v>
       </c>
-      <c r="B31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36" s="4"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39" s="4"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A34:B34"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -899,7 +822,7 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -919,174 +842,550 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
+      <c r="B2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D2" s="2">
         <v>-1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
+      <c r="E2" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
+      <c r="B3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D3" s="2">
         <v>-1</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
+      <c r="E3" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
+      <c r="B4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D4" s="2">
         <v>-1</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
+      <c r="E4" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Line/config.xlsx
+++ b/Line/config.xlsx
@@ -67,16 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,109 +439,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>나이</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
           <t>내러티브</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>**서울 대단지 아파트**에 거주하며, 방학마다 **해외여행**을 갈 수 있고, 원하는 학원을 **마음껏** 다닐 수 있는 **비장애인** 학생.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>나는 15살 {성별}이며, **서울 대단지 아파트**에 거주하며 방학마다 **해외여행**을 갈 수 있고, 원하는 학원을 **마음껏** 다닐 수 있는 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>**지방 소도시 다세대주택**에 거주하며, 형편에 맞춰 학원을 골라야 하고, **한부모 가정**에서 자란 **비장애인** 학생.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>나는 14살 {성별}이며, **지방 소도시 다세대주택**에 거주하며 형편에 맞춰 학원을 골라야 하고, **한부모 가정**에서 자란 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>**농어촌 마을**에 거주하며, 필요한 물건은 대부분 살 수 있고, **다문화가정**에서 자란 **비장애인** 학생.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>나는 13살 {성별}이며, **농어촌 마을**에 거주하며 필요한 물건은 대부분 살 수 있고, **다문화가정**에서 자란 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>형편이 어려워 **아르바이트**를 해야 하고, 학원을 거의 다니지 못하며, **조부모님과 함께 사는** 학생.</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>나는 15살 {성별}이며, 형편이 어려워 **아르바이트**를 해야 하고, 학원을 거의 다니지 못하며, **조부모님과 함께 사는** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>**신체적 장애**가 있고, 부모님과 함께 살며, 방학마다 해외여행을 갈 수 있는 학생.</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>나는 14살 {성별}이며, **신체적 장애**가 있고, 부모님과 함께 살며, 방학마다 해외여행을 갈 수 있는 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>**새터민 가정** 출신이며, 형편에 맞춰 학원을 골라야 하고, 발달 장애가 있는 형제와 함께 자란 학생.</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>나는 13살 {성별}이며, **새터민 가정** 출신이고, 형편에 맞춰 학원을 골라야 하며, 발달 장애가 있는 형제와 함께 자란 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>**해외에서 거주하다 최근 귀국**했고, 원하는 학원을 마음껏 다닐 수 있으며, 부모님과 함께 사는 **비장애인** 학생.</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>나는 15살 {성별}이며, **해외에서 거주하다 최근 귀국**했고, 원하는 학원을 마음껏 다닐 수 있으며, 부모님과 함께 사는 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>형편이 어려워 아르바이트를 해야 하고, **다문화가정**에서 자랐으며, 신체적 장애가 있는 학생.</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>나는 14살 {성별}이며, 형편이 어려워 아르바이트를 해야 하고, **다문화가정**에서 자랐으며, 신체적 장애가 있는 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>※ 한 행 = 완성된 캐릭터 한 명. 활동 시작 시 이 목록에서 겹치지 않게 무작위로 한 명씩 배정됩니다.</t>
+          <t>※ 한 행 = 완성된 배경 서사 한 개. 활동 시작 시 이 목록에서 겹치지 않게 무작위로 한 명씩 배정됩니다.</t>
         </is>
       </c>
     </row>
@@ -565,41 +532,25 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>※ 나이: 그 캐릭터의 나이(숫자만). 학생 화면에는 '나는 중학교에 재학 중인 15살 여학생이다.'처럼</t>
+          <t>※ {성별} 자리에는 학생이 입장 시 직접 선택한 성별("남" 또는 "여")이 그대로 들어갑니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   성별(학생이 입장 시 직접 선택)과 자동으로 합쳐져 문장 맨 앞에 표시됩니다.</t>
+          <t xml:space="preserve">   원하는 위치에 자유롭게 넣으세요. 나이도 원하시면 이 문장 안에 직접 적어주세요 (예: "나는 15살...").</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>※ 내러티브: 그 뒤에 이어질 나머지 문장. **이렇게** 별 두 개로 감싸면 그 부분만 진하게(볼드) 표시됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>※ 성별과 나이는 학생마다 다르게 배정되지만, 실제 학생의 성별과는 무관하게 캐릭터 설정일 뿐입니다.</t>
+          <t>※ **이렇게** 별 두 개로 감싸면 그 부분만 진하게(볼드) 표시됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:B12"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -844,11 +795,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,24 +817,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>오프닝문장</t>
+          <t>활동안내</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>나는 중학교에 재학 중인 {나이}살 {성별}학생이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>안내문구</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>1. 여러분에게는 무작위로 정해진 가상의 캐릭터(또는 실제 자신의 상황)가 주어집니다.
+          <t>1. 여러분에게는 무작위로 정해진 배경 이야기(또는 실제 자신의 상황)가 주어집니다.
 2. 선생님이 질문을 하나씩 제시하면, 자신의 조건에 비추어 두 선택지 중 하나를 골라 확정해주세요.
 3. 선택에 따라 화면 속 나의 위치가 앞뒤로 움직입니다.
 4. 옆 친구와 위치를 비교하며 놀리거나 장난치지 않도록 유의해주세요.
@@ -891,57 +830,24 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>※ 활동안내: [활동 시작] 직후 교사 화면(예: TV)에 표시되는 활동 방법 안내문입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>※ 오프닝문장: 캐릭터 문장 맨 앞에 붙는 성별·나이 소개 문장입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>※ {나이}와 {성별} 자리에 각각 캐릭터의 나이와 학생이 입장 시 선택한 성별이 자동으로 들어갑니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>※ 자유롭게 문구를 바꿔도 되고, {나이}/{성별} 토큰의 위치도 원하는 대로 옮길 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  예: "{성별}학생인 나는 {나이}살, 중학교 2학년이다."</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>※ {성별}은 "남" 또는 "여"로만 채워집니다 ("남학생"이 아님) — "학생" 등은 템플릿에 직접 적어주세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>※ 안내문구: 활동 시작 직후 교사 화면(예: TV)에 표시되는 놀이 방법·유의사항 안내문입니다. 줄바꿈해서 여러 줄로 적을 수 있습니다.</t>
+          <t xml:space="preserve">   줄바꿈(Alt+Enter)으로 여러 줄을 적을 수 있습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="2">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Line/config.xlsx
+++ b/Line/config.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="personas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="guide" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,70 +439,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>내러티브</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>나는 15살 {성별}이며, **서울 대단지 아파트**에 거주하며 방학마다 **해외여행**을 갈 수 있고, 원하는 학원을 **마음껏** 다닐 수 있는 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>나는 14살 {성별}이며, **지방 소도시 다세대주택**에 거주하며 형편에 맞춰 학원을 골라야 하고, **한부모 가정**에서 자란 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>나는 13살 {성별}이며, **농어촌 마을**에 거주하며 필요한 물건은 대부분 살 수 있고, **다문화가정**에서 자란 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>나는 15살 {성별}이며, 형편이 어려워 **아르바이트**를 해야 하고, 학원을 거의 다니지 못하며, **조부모님과 함께 사는** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>나는 14살 {성별}이며, **신체적 장애**가 있고, 부모님과 함께 살며, 방학마다 해외여행을 갈 수 있는 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>나는 13살 {성별}이며, **새터민 가정** 출신이고, 형편에 맞춰 학원을 골라야 하며, 발달 장애가 있는 형제와 함께 자란 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>나는 15살 {성별}이며, **해외에서 거주하다 최근 귀국**했고, 원하는 학원을 마음껏 다닐 수 있으며, 부모님과 함께 사는 **비장애인** 학생이다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>나는 14살 {성별}이며, 형편이 어려워 아르바이트를 해야 하고, **다문화가정**에서 자랐으며, 신체적 장애가 있는 학생이다.</t>
         </is>
@@ -511,46 +541,62 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>※ 한 행 = 완성된 배경 서사 한 개. 활동 시작 시 이 목록에서 겹치지 않게 무작위로 한 명씩 배정됩니다.</t>
+          <t>※ 순번: 그냥 보기 편하라고 매기는 번호일 뿐, 배정 순서와는 무관합니다 (무작위로 섞여서 배정됩니다).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>※ 정원(입장 가능 인원)은 이 행의 개수로 자동 정해집니다. 예: 30행을 적으면 최대 30명까지 입장 가능.</t>
+          <t>※ 한 행 = 완성된 배경 서사 한 개. 활동 시작 시 이 목록에서 겹치지 않게 무작위로 한 명씩 배정됩니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (학급 인원수에 맞춰 행을 넉넉히 추가해주세요)</t>
+          <t>※ 정원(입장 가능 인원)은 이 행의 개수로 자동 정해집니다. 예: 30행을 적으면 최대 30명까지 입장 가능.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>※ {성별} 자리에는 학생이 입장 시 직접 선택한 성별("남" 또는 "여")이 그대로 들어갑니다.</t>
+          <t xml:space="preserve">  (학급 인원수에 맞춰 행을 넉넉히 추가해주세요)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   원하는 위치에 자유롭게 넣으세요. 나이도 원하시면 이 문장 안에 직접 적어주세요 (예: "나는 15살...").</t>
+          <t>※ {성별} 자리에는 학생이 입장 시 직접 선택한 성별("남" 또는 "여")이 그대로 들어갑니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   원하는 위치에 자유롭게 넣으세요. 나이도 원하시면 이 문장 안에 직접 적어주세요 (예: "나는 15살...").</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>※ **이렇게** 별 두 개로 감싸면 그 부분만 진하게(볼드) 표시됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -795,59 +841,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>항목</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>활동안내</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1. 여러분에게는 무작위로 정해진 배경 이야기(또는 실제 자신의 상황)가 주어집니다.
-2. 선생님이 질문을 하나씩 제시하면, 자신의 조건에 비추어 두 선택지 중 하나를 골라 확정해주세요.
-3. 선택에 따라 화면 속 나의 위치가 앞뒤로 움직입니다.
-4. 옆 친구와 위치를 비교하며 놀리거나 장난치지 않도록 유의해주세요.
-5. 활동이 끝나면 나의 최종 위치와 반 전체에서의 순위를 확인할 수 있습니다.</t>
+          <t>여러분에게는 무작위로 정해진 배경 이야기(또는 실제 자신의 상황)가 주어집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>선생님이 질문을 하나씩 제시하면, 자신의 조건에 비추어 두 선택지 중 하나를 골라 확정해주세요.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>※ 활동안내: [활동 시작] 직후 교사 화면(예: TV)에 표시되는 활동 방법 안내문입니다.</t>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>선택에 따라 화면 속 나의 위치가 앞뒤로 움직입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   줄바꿈(Alt+Enter)으로 여러 줄을 적을 수 있습니다.</t>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>옆 친구와 위치를 비교하며 놀리거나 장난치지 않도록 유의해주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>활동이 끝나면 나의 최종 위치와 반 전체에서의 순위를 확인할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>※ 순번 순서대로 한 줄씩 이어져서 활동 안내 화면에 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>※ 행을 추가/삭제해서 안내 줄 수를 자유롭게 조정할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>※ 이 시트가 없으면 기본 안내문이 사용됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Line/config.xlsx
+++ b/Line/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\social-starting-line\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FD28F0-99F7-4049-B67D-AAB2766B06F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6334B75-0DC3-434E-9257-DDDBC3DEB8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2316,17 +2316,24 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>‘조건’에</t>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>**②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 조건과</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
-        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2337,6 +2344,358 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>질문을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비웃거나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장난치지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:**
+“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">?” </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되묻기나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>친구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부르기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등…
+가상의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조건이지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>친구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누군가가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처받을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> '조건’에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>진지하게</t>
     </r>
     <r>
@@ -2379,7 +2738,8 @@
         <rFont val="Arial"/>
         <family val="3"/>
       </rPr>
-      <t>:_x000B_</t>
+      <t xml:space="preserve">:**
+</t>
     </r>
     <r>
       <rPr>
@@ -2525,354 +2885,6 @@
         <charset val="129"/>
       </rPr>
       <t>생각</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조건과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비웃거나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장난치지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:_x000B_“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">?” </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>되묻기나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>친구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이름</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부르기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_x000B_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가상의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조건이지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>친구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누군가가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>크게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상처받을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있음</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2881,7 +2893,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2938,6 +2950,11 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2975,7 +2992,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4090,20 +4109,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="52.2" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">

--- a/Line/config.xlsx
+++ b/Line/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b1gi5m\Desktop\social-starting-line\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD7C4EA-40C7-498F-98EB-AB1EC3D82C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A28EB2-37FB-4D69-BEB4-A016F6E665E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="1860" windowWidth="21600" windowHeight="11505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>내용</t>
   </si>
   <si>
-    <t>새 핸드폰이나 새 옷을 사고 싶을 때 비싼 가격 때문에 걱정한 적이…</t>
-  </si>
-  <si>
     <t>있다</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
   </si>
   <si>
     <t>외모 때문에 다른 사람들에게 한국인이 맞냐는 차별적 시선을 받은 적이…</t>
-  </si>
-  <si>
-    <t>관심 있는 분야가 있어도 배울 수 있는 학원이 집 근처에 없어 멀리 가야 했던 적이…</t>
   </si>
   <si>
     <t>학교가 끝나고 집에 돌아갔을 때 나를 챙겨줄 어른이…</t>
@@ -2908,6 +2902,14 @@
       </rPr>
       <t>있음</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>관심 있는 분야가 있어도 보통 배울 수 있는 학원이 집 근처에…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>새 핸드폰이나 새 옷을 사고 싶을 때 비싼 가격 때문에 걱정한 적이…</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2915,7 +2917,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2997,6 +2999,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3023,7 +3030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3037,6 +3044,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3359,10 +3367,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="99">
@@ -3370,10 +3378,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="99">
@@ -3381,10 +3389,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="82.5">
@@ -3392,10 +3400,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="99">
@@ -3403,10 +3411,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="99">
@@ -3414,10 +3422,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="66">
@@ -3425,10 +3433,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="132">
@@ -3436,10 +3444,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="82.5">
@@ -3447,10 +3455,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="99">
@@ -3458,10 +3466,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="99">
@@ -3469,10 +3477,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="82.5">
@@ -3480,10 +3488,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="99">
@@ -3491,10 +3499,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="82.5">
@@ -3502,10 +3510,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="99">
@@ -3513,10 +3521,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="99">
@@ -3524,10 +3532,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="115.5">
@@ -3535,10 +3543,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="99">
@@ -3546,10 +3554,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="82.5">
@@ -3557,10 +3565,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="99">
@@ -3568,10 +3576,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="115.5">
@@ -3579,10 +3587,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="99">
@@ -3590,10 +3598,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="82.5">
@@ -3601,10 +3609,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="99">
@@ -3612,10 +3620,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="99">
@@ -3623,10 +3631,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="132">
@@ -3634,10 +3642,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="99">
@@ -3645,10 +3653,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="99">
@@ -3656,10 +3664,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="99">
@@ -3667,10 +3675,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="99">
@@ -3678,10 +3686,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3696,7 +3704,7 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="2" max="2" width="66.75" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -3728,19 +3736,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3748,16 +3756,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>-1</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -3768,16 +3776,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -3788,19 +3796,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>-1</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3808,19 +3816,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="F6" s="2">
         <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3828,16 +3836,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F7" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3845,16 +3856,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>-1</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3862,16 +3876,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3879,16 +3896,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3896,16 +3916,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>-1</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3913,16 +3936,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3930,16 +3956,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F13" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3947,16 +3976,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="F14" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3964,16 +3996,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>-1</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3981,101 +4016,119 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>-1</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>-1</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>27</v>
+      </c>
+      <c r="F18" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>36</v>
+      </c>
+      <c r="F19" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>-1</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4106,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="49.5">
@@ -4114,7 +4167,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/Line/config.xlsx
+++ b/Line/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b1gi5m\Desktop\social-starting-line\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b1gi5m\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A28EB2-37FB-4D69-BEB4-A016F6E665E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB5E539-84FD-4C0D-AFED-BDB06F5C4FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1860" windowWidth="21600" windowHeight="11505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personas" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="105">
   <si>
     <t>순번</t>
   </si>
@@ -57,9 +57,6 @@
     <t>없다</t>
   </si>
   <si>
-    <t>졸업식, 공개수업 등 학교 행사에 보호자가 참석하지 못해 친구들 사이에서 위축된 적이…</t>
-  </si>
-  <si>
     <t>치아 교정이나 피부 관리 등 꼭 필요하진 않지만 꽤 비용이 드는 치료를 받아본 적이…</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>드물다</t>
   </si>
   <si>
-    <t>생활비를 벌거나 가족을 돌보느라 온전한 나만의 시간을 포기해야 했던 적이…</t>
-  </si>
-  <si>
     <t>막차 시간 때문에 친구들과 더 놀고 싶어도 아쉽게 일찍 일어나야 했던 경험이…</t>
   </si>
   <si>
@@ -193,6 +187,9 @@
     <t>상 (서울, 의사, 외벌이, 전업주부, 돌봄 가능)</t>
   </si>
   <si>
+    <t>상 (신도시, 대기업 관리자, 공공기관, 맞벌이)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
     </r>
@@ -206,7 +203,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>경기도의 신도시</t>
+      <t>서울</t>
     </r>
     <r>
       <rPr>
@@ -228,17 +225,809 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>대기업에서 관리자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">로 일하시고, 어머니는 </t>
+      <t>대학 교수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이고 어머니는 집에서 가족을 돌보신다. 아버지는 다른 직장인보다 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>출퇴근 시간을 조절하기 쉬운 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이라 학교 행사나 내가 도움이 필요할 때 시간을 내 주시는 경우가 많다.</t>
+    </r>
+  </si>
+  <si>
+    <t>상 (서울, 교수, 외벌이, 전업주부, 시간 여유)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>세종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>외교관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이라 한국에서 근무하고 계시고, 나는 아버지의 근무 때문에 어릴 때 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>캐나다에서 한국으로 이사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왔다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>피부색이 조금 밝고 눈과 코 생김새가 한국 친구들과 조금 다른 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이며, 어머니는 집에서 나와 동생을 돌보신다.</t>
+    </r>
+  </si>
+  <si>
+    <t>상 (세종, 외교관, 서양 출신 이주, 전업주부)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변호사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>약사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>라 두 분 모두 전문직으로 일하신다. 일이 바쁜 시기도 있지만 각자 시간을 조절할 수 있는 편이라 가족에게 필요한 일이 생기면 한 분이 시간을 내는 경우가 많다.</t>
+    </r>
+  </si>
+  <si>
+    <t>상 (부산, 변호사, 약사, 전문직 맞벌이, 돌봄 가능)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시청 공무원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">으로 일하시고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회사원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이다. 두 분 모두 평일에 일정한 시간에 출퇴근하는 편이라 평소에는 저녁에 가족이 함께 식사하는 날이 많다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (대전, 공무원, 회사원, 맞벌이, 돌봄 보통)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다른 지역에서 건축사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">로 일해서 평일에는 그곳에서 지내고 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주말에 집으로 돌아오신다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 어머니는 학교 교사라 평일에는 학교가 끝난 뒤 내가 집에 돌아왔을 때 함께 있는 경우가 많다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (부산, 주말부부, 건축사, 교사)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>인천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우체국에서 일하시고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중국에서 한국으로 와서 작은 식당을 운영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">하신다. 어머니를 닮아 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>피부색과 눈매가 한국 친구들과 조금 다른 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이고, 부모님 모두 일하는 시간이 길어 학교가 끝난 뒤 혼자 집에 있는 날도 있다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (인천, 중국계, 우체국 직원, 식당 운영, 맞벌이, 방과 후 혼자)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>세종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 회사원이고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>병원 간호사로 교대근무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>를 하신다. 어머니가 밤이나 이른 아침에 근무하는 날에는 아버지가 집안일과 나를 챙기는 일을 맡는 식으로 두 분이 시간을 맞춰 생활한다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (세종, 회사원, 간호사, 교대근무, 맞벌이)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대구에서 어머니와 단둘이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 살고 있다. 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공공기관에서 정해진 시간에 근무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하시고, 퇴근하면 집에서 나와 함께 저녁을 먹으며 학교 이야기를 들어 주신다. 가족이 둘뿐이라 집안의 일은 대부분 어머니와 내가 나누어 한다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (대구, 한부모, 공공기관, 안정적 근무, 돌봄 가능)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>광주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자동차 정비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 일을 하시고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>미용실</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에서 일하신다. 두 분 모두 평일에도 늦게까지 일하는 날이 있어서 학교가 끝난 뒤 바로 집에 오지 못하고 시간을 보내는 날이 가끔 있다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (광주, 기술직, 미용사, 맞벌이, 늦은 퇴근)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경기도의 한 도시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공인중개사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">로 일하시고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중학교 교사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다. 아버지는 주말에도 손님을 만나는 일이 있지만 평일에는 비교적 시간을 조절할 수 있어 학교에 필요한 일이 생기면 도움을 받을 수 있다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (경기, 공인중개사, 교사, 근무시간 차이)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>호텔에서 일하시고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 어머니는 집 근처에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>작은 가게를 운영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하신다. 관광객이 많은 시기에는 두 분 모두 바빠지지만, 가게가 한산한 시간에는 어머니가 집에 돌아와 나를 챙기기도 한다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (제주, 호텔 근무, 자영업, 맞벌이, 계절적 바쁨)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>충북의 한 도시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
     </r>
     <r>
       <rPr>
@@ -260,11 +1049,55 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>에서 일하신다. 두 분 모두 직장이 안정적인 편이고, 바쁜 날에는 서로 시간을 맞춰 집안일과 나를 돌보는 일을 나누신다.</t>
-    </r>
-  </si>
-  <si>
-    <t>상 (신도시, 대기업 관리자, 공공기관, 맞벌이)</t>
+      <t xml:space="preserve">에서 일하시고, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일본에서 한국으로 오신 어머니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">는 번역 일을 시간제로 하고 계신다. 어머니를 닮아 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>눈매와 머리카락 생김새가 한국 친구들과 조금 다른 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이며, 어머니는 일을 하지 않는 시간에는 집에서 나를 챙기신다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (충북, 일본계, 공공기관, 시간제 근무)</t>
   </si>
   <si>
     <r>
@@ -280,7 +1113,59 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>서울</t>
+      <t>서울에서 아버지와 둘이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>항공사에서 일하시는데 지방이나 해외 출장이 있는 날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이 가끔 있다. 출장이나 늦은 퇴근이 겹치면 학교가 끝난 뒤 혼자 시간을 보내지만, 평소에는 아버지가 퇴근해서 함께 생활한다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (서울, 한부모, 항공사, 출장, 방과 후 혼자)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부산</t>
     </r>
     <r>
       <rPr>
@@ -302,43 +1187,68 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>대학 교수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이고 어머니는 집에서 가족을 돌보신다. 아버지는 다른 직장인보다 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>출퇴근 시간을 조절하기 쉬운 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이라 학교 행사나 내가 도움이 필요할 때 시간을 내 주시는 경우가 많다.</t>
-    </r>
-  </si>
-  <si>
-    <t>상 (서울, 교수, 외벌이, 전업주부, 시간 여유)</t>
+      <t>고등학교 교사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>캐나다에서 한국으로 와서 온라인으로 영어 수업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">을 하고 계신다. 어머니를 닮아 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>피부색과 눈·코 생김새가 한국 친구들과 조금 다른 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이지만, 부모님은 모두 집에서 일하는 시간을 조절할 수 있어 학교가 끝난 뒤에도 가족이 함께 보내는 시간이 있다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (부산, 서양계 국결, 교사, 재택·시간제, 돌봄 가능)</t>
+  </si>
+  <si>
+    <t>중 (대전, 연구원, 병원 근무, 교대·시간 차이, 조부모 돌봄)</t>
   </si>
   <si>
     <r>
@@ -364,6 +1274,58 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 일반 회사원이고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>집에서 가족을 돌보신다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 아버지가 야근하는 날도 있지만 평소에는 어머니가 집에 계셔서 학교에서 돌아온 뒤 혼자 지내는 일이 많지 않다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (세종, 회사원, 외벌이, 전업주부, 돌봄 가능)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경남의 한 공업도시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
     </r>
     <r>
@@ -376,65 +1338,43 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>외교관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이라 한국에서 근무하고 계시고, 나는 아버지의 근무 때문에 어릴 때 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>캐나다에서 한국으로 이사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 왔다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>피부색이 조금 밝고 눈과 코 생김새가 한국 친구들과 조금 다른 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이며, 어머니는 집에서 나와 동생을 돌보신다.</t>
-    </r>
-  </si>
-  <si>
-    <t>상 (세종, 외교관, 서양 출신 이주, 전업주부)</t>
+      <t>공장에서 교대근무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">를 하고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사회복지사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로 일하신다. 아버지가 밤에 일하는 주에는 어머니가 집안일을 더 맡고, 아버지가 쉬는 날에는 반대로 집안일과 나를 돌보는 일을 나누어 한다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (경남, 공장 근무, 사회복지사, 교대근무)</t>
   </si>
   <si>
     <r>
@@ -450,6 +1390,193 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>전북의 작은 도시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>농산물 유통</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 일을 하시고 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초등학교에서 행정 업무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>를 하신다. 두 분 모두 일정한 시간에 일하는 편이라 학교가 끝난 뒤에는 번갈아 집에 있는 경우가 많다.</t>
+    </r>
+  </si>
+  <si>
+    <t>중 (전북, 농산물 유통, 학교 행정, 맞벌이, 돌봄 보통)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>강원도의 하루에 시내버스가 두 번밖에 오지 않는 산골 마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 회사에 다니지만 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>집에서 직장까지 거리가 멀어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 아침 일찍 나가고 늦게 돌아오시는 날이 많다. 어머니는 집에서 농사일과 집안일을 하신다.</t>
+    </r>
+  </si>
+  <si>
+    <t>하 (강원 산골, 제한된 교통, 장거리 출퇴근, 전업주부)</t>
+  </si>
+  <si>
+    <t>하 (전남 섬, 제한된 교통, 어업, 불규칙 근무)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경북의 한 도시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 나는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다리가 불편해서 휠체어가 없으면 이동이 어렵다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 아버지는 회사원이고 어머니는 초등학교 교사라 두 분 모두 일을 하시지만, 학교나 외출과 관련해 내가 도움이 필요할 때는 부모님이 시간을 맞춰 도와주신다.</t>
+    </r>
+  </si>
+  <si>
+    <t>하 (경북, 지체장애, 회사원·교사, 맞벌이)</t>
+  </si>
+  <si>
+    <t>하 (대전, 난민 배경, 이주, 공장 근무, 전업주부)</t>
+  </si>
+  <si>
+    <t>하 (전북 농촌, 필리핀계, 농업, 가족 공동 노동)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>부산</t>
     </r>
     <r>
@@ -472,43 +1599,68 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>변호사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>약사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>라 두 분 모두 전문직으로 일하신다. 일이 바쁜 시기도 있지만 각자 시간을 조절할 수 있는 편이라 가족에게 필요한 일이 생기면 한 분이 시간을 내는 경우가 많다.</t>
-    </r>
-  </si>
-  <si>
-    <t>상 (부산, 변호사, 약사, 전문직 맞벌이, 돌봄 가능)</t>
+      <t>화물차 운전기사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이고, 가나에서 한국으로 온 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공장에서 일하신다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. 아버지는 일 때문에 집을 비우는 시간이 길고 어머니도 교대시간에 따라 근무해서 두 분의 시간이 맞지 않는 날에는 학교가 끝난 뒤 혼자 지내기도 한다. 어머니를 닮아 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>피부색이 조금 짙고 머리카락이 곱슬한 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이다.</t>
+    </r>
+  </si>
+  <si>
+    <t>하 (부산, 가나계, 운전직·공장 근무, 근무시간 불규칙, 방과 후 혼자)</t>
+  </si>
+  <si>
+    <t>하 (대구, 청각장애, 외벌이, 전업주부, 돌봄 가능)</t>
   </si>
   <si>
     <r>
@@ -524,7 +1676,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>대전</t>
+      <t>경기도의 한 도시</t>
     </r>
     <r>
       <rPr>
@@ -546,43 +1698,43 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>시청 공무원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">으로 일하시고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>회사원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이다. 두 분 모두 평일에 일정한 시간에 출퇴근하는 편이라 평소에는 저녁에 가족이 함께 식사하는 날이 많다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (대전, 공무원, 회사원, 맞벌이, 돌봄 보통)</t>
+      <t>개인 택배 일을 하시고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 어머니는 병원에서 행정직으로 일하신다. 두 분 모두 일하는 시간이 길고 일정하지 않은 편이라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>학교가 끝난 뒤 부모님이 아직 집에 오지 않은 날이 자주 있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>하 (경기, 택배업, 병원 행정, 맞벌이, 돌봄 부족)</t>
   </si>
   <si>
     <r>
@@ -598,7 +1750,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>부산</t>
+      <t>인천</t>
     </r>
     <r>
       <rPr>
@@ -620,1546 +1772,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>다른 지역에서 건축사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">로 일해서 평일에는 그곳에서 지내고 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>주말에 집으로 돌아오신다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. 어머니는 학교 교사라 평일에는 학교가 끝난 뒤 내가 집에 돌아왔을 때 함께 있는 경우가 많다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (부산, 주말부부, 건축사, 교사)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>인천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>우체국에서 일하시고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>중국에서 한국으로 와서 작은 식당을 운영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">하신다. 어머니를 닮아 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>피부색과 눈매가 한국 친구들과 조금 다른 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이고, 부모님 모두 일하는 시간이 길어 학교가 끝난 뒤 혼자 집에 있는 날도 있다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (인천, 중국계, 우체국 직원, 식당 운영, 맞벌이, 방과 후 혼자)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>세종</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 회사원이고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>병원 간호사로 교대근무</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>를 하신다. 어머니가 밤이나 이른 아침에 근무하는 날에는 아버지가 집안일과 나를 챙기는 일을 맡는 식으로 두 분이 시간을 맞춰 생활한다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (세종, 회사원, 간호사, 교대근무, 맞벌이)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>대구에서 어머니와 단둘이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 살고 있다. 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공공기관에서 정해진 시간에 근무</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>하시고, 퇴근하면 집에서 나와 함께 저녁을 먹으며 학교 이야기를 들어 주신다. 가족이 둘뿐이라 집안의 일은 대부분 어머니와 내가 나누어 한다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (대구, 한부모, 공공기관, 안정적 근무, 돌봄 가능)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>광주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자동차 정비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 일을 하시고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>미용실</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>에서 일하신다. 두 분 모두 평일에도 늦게까지 일하는 날이 있어서 학교가 끝난 뒤 바로 집에 오지 못하고 시간을 보내는 날이 가끔 있다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (광주, 기술직, 미용사, 맞벌이, 늦은 퇴근)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>경기도의 한 도시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공인중개사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">로 일하시고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>중학교 교사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다. 아버지는 주말에도 손님을 만나는 일이 있지만 평일에는 비교적 시간을 조절할 수 있어 학교에 필요한 일이 생기면 도움을 받을 수 있다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (경기, 공인중개사, 교사, 근무시간 차이)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>호텔에서 일하시고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 어머니는 집 근처에서 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>작은 가게를 운영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>하신다. 관광객이 많은 시기에는 두 분 모두 바빠지지만, 가게가 한산한 시간에는 어머니가 집에 돌아와 나를 챙기기도 한다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (제주, 호텔 근무, 자영업, 맞벌이, 계절적 바쁨)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>충북의 한 도시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공공기관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 일하시고, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일본에서 한국으로 오신 어머니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">는 번역 일을 시간제로 하고 계신다. 어머니를 닮아 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>눈매와 머리카락 생김새가 한국 친구들과 조금 다른 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이며, 어머니는 일을 하지 않는 시간에는 집에서 나를 챙기신다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (충북, 일본계, 공공기관, 시간제 근무)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>서울에서 아버지와 둘이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>항공사에서 일하시는데 지방이나 해외 출장이 있는 날</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이 가끔 있다. 출장이나 늦은 퇴근이 겹치면 학교가 끝난 뒤 혼자 시간을 보내지만, 평소에는 아버지가 퇴근해서 함께 생활한다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (서울, 한부모, 항공사, 출장, 방과 후 혼자)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>고등학교 교사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>캐나다에서 한국으로 와서 온라인으로 영어 수업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">을 하고 계신다. 어머니를 닮아 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>피부색과 눈·코 생김새가 한국 친구들과 조금 다른 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이지만, 부모님은 모두 집에서 일하는 시간을 조절할 수 있어 학교가 끝난 뒤에도 가족이 함께 보내는 시간이 있다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (부산, 서양계 국결, 교사, 재택·시간제, 돌봄 가능)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>대전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>연구소 연구원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이고 어머니는 병원에서 일하신다. 두 분의 근무시간이 맞지 않는 날에는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>외할머니가 학교가 끝난 뒤 집에 와서 나와 동생을 돌봐 주신다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (대전, 연구원, 병원 근무, 교대·시간 차이, 조부모 돌봄)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>세종</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 일반 회사원이고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>집에서 가족을 돌보신다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. 아버지가 야근하는 날도 있지만 평소에는 어머니가 집에 계셔서 학교에서 돌아온 뒤 혼자 지내는 일이 많지 않다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (세종, 회사원, 외벌이, 전업주부, 돌봄 가능)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>경남의 한 공업도시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공장에서 교대근무</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">를 하고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사회복지사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>로 일하신다. 아버지가 밤에 일하는 주에는 어머니가 집안일을 더 맡고, 아버지가 쉬는 날에는 반대로 집안일과 나를 돌보는 일을 나누어 한다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (경남, 공장 근무, 사회복지사, 교대근무)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>전북의 작은 도시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>농산물 유통</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 일을 하시고 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>초등학교에서 행정 업무</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>를 하신다. 두 분 모두 일정한 시간에 일하는 편이라 학교가 끝난 뒤에는 번갈아 집에 있는 경우가 많다.</t>
-    </r>
-  </si>
-  <si>
-    <t>중 (전북, 농산물 유통, 학교 행정, 맞벌이, 돌봄 보통)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>강원도의 하루에 시내버스가 두 번밖에 오지 않는 산골 마을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 회사에 다니지만 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>집에서 직장까지 거리가 멀어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 아침 일찍 나가고 늦게 돌아오시는 날이 많다. 어머니는 집에서 농사일과 집안일을 하신다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (강원 산골, 제한된 교통, 장거리 출퇴근, 전업주부)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>전라남도의 육지에 나가기 위해 배를 타야 하는 작은 섬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>어업에 종사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>하시고 어머니는 집안일을 하신다. 아버지는 날씨와 바다 상황에 따라 일하는 시간이 달라서 가족의 생활시간도 일정하지 않은 편이다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (전남 섬, 제한된 교통, 어업, 불규칙 근무)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>경북의 한 도시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 나는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다리가 불편해서 휠체어가 없으면 이동이 어렵다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. 아버지는 회사원이고 어머니는 초등학교 교사라 두 분 모두 일을 하시지만, 학교나 외출과 관련해 내가 도움이 필요할 때는 부모님이 시간을 맞춰 도와주신다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (경북, 지체장애, 회사원·교사, 맞벌이)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>대전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 부모님은 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>전쟁을 피해 다른 나라에서 한국으로 와 난민으로 인정받았고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, 아버지는 공장에서 일하시며 어머니는 집에서 가족을 돌보신다. 집에서는 부모님이 익숙한 언어를 사용하는 경우가 있고, 나는 학교에서 주로 한국어를 사용한다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (대전, 난민 배경, 이주, 공장 근무, 전업주부)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>전라북도의 농촌 마을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>농사를 짓고 계시고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, 필리핀에서 한국으로 오신 어머니도 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>함께 농사일을 돕고 계신다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. 나 역시 농번기에는 학교에서 돌아온 뒤 부모님의 일을 조금씩 돕는다. 어머니를 닮아 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>피부색이 조금 짙고 눈매가 한국 친구들과 조금 다른 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (전북 농촌, 필리핀계, 농업, 가족 공동 노동)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>화물차 운전기사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이고, 가나에서 한국으로 온 어머니는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>공장에서 일하신다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. 아버지는 일 때문에 집을 비우는 시간이 길고 어머니도 교대시간에 따라 근무해서 두 분의 시간이 맞지 않는 날에는 학교가 끝난 뒤 혼자 지내기도 한다. 어머니를 닮아 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>피부색이 조금 짙고 머리카락이 곱슬한 편</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (부산, 가나계, 운전직·공장 근무, 근무시간 불규칙, 방과 후 혼자)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>대구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 나는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>청각장애가 있어 다른 사람의 말을 들을 때 도움이 필요한 경우가 있다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. 아버지는 회사에서 정해진 시간에 일하시고 어머니는 집에서 가족을 돌보셔서 학교가 끝난 뒤에는 어머니와 함께 있는 시간이 많다.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (대구, 청각장애, 외벌이, 전업주부, 돌봄 가능)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>경기도의 한 도시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>개인 택배 일을 하시고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 어머니는 병원에서 행정직으로 일하신다. 두 분 모두 일하는 시간이 길고 일정하지 않은 편이라 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>학교가 끝난 뒤 부모님이 아직 집에 오지 않은 날이 자주 있다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>하 (경기, 택배업, 병원 행정, 맞벌이, 돌봄 부족)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>인천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>일용직으로 건설 현장</t>
     </r>
     <r>
@@ -2219,77 +1831,6 @@
   </si>
   <si>
     <t>하 (인천, 일용직, 시간제, 불규칙 근무, 돌봄 부족)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>전북의 농촌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 조부모님과 살고 있다. 부모님은 여러 사정으로 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>나를 직접 돌볼 수 없어 어릴 때부터 조부모님이 나를 키워 오셨다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. 나는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시각장애가 있어 혼자 이동할 때 주변 상황을 확인하는 데 도움이 필요한 경우</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>가 있고, 평소에는 조부모님과 함께 생활한다.</t>
-    </r>
   </si>
   <si>
     <t>하 (전북 농촌, 조손가정, 부모 돌봄 부재, 시각장애)</t>
@@ -2910,6 +2451,482 @@
   </si>
   <si>
     <t>새 핸드폰이나 새 옷을 사고 싶을 때 비싼 가격 때문에 걱정한 적이…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전라북도의 농촌 마을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>농사를 짓고 계시고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 필리핀에서 한국으로 오신 어머니도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>함께 농사일을 돕고 계신다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. 어머니를 닮아 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>피부색이 조금 짙고 눈매가 한국 친구들과 조금 다른 편</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이다.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경기도의 신도시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대기업에서 임원으</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">로 일하시고, 어머니는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>공공기관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에서 일하신다. 두 분 모두 직장이 안정적인 편이고, 바쁜 날에는 서로 시간을 맞춰 집안일과 나를 돌보는 일을 나누신다.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연구원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이고 어머니는 병원에서 일하신다. 두 분의 근무시간이 맞지 않는 날에는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>외할머니가 학교가 끝난 뒤 집에 와서 나와 동생을 돌봐 주신다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전라남도의 육지에 나가기 위해서는 배를 타야 하는 작은 섬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 아버지는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>어업에 종사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하시고 어머니는 집안일을 하신다. 아버지는 날씨와 바다 상황에 따라 일하는 시간이 달라서 가족의 생활시간도 일정하지 않은 편이다.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원래 살던 나라에서 내전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을 피해 한국으로 온 난민이다.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 아버지는 공장에서 일하시며 어머니는 집에서 가족을 돌보신다. 원래 사용하던 언어에는 익숙하지만, 한국어를 사용하는 데는 아직 미숙하다.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 부모님과 살고 있다. 나는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>청각장애가 있어 수화를 이용해야 다른 사람과 대화할 수 있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 아버지는 회사에서 정해진 시간에 일하시고 어머니는 집에서 가족을 돌보셔서 학교가 끝난 뒤에는 어머니와 함께 있는 시간이 많다.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나는 15살 {성별}학생이다. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전북의 농촌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 조부모님과 살고 있다. 부모님은 여러 사정으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>나를 직접 돌볼 수 없어 어릴 때부터 조부모님이 나를 키워 오셨다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. 나는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">시각장애가 있어 앞을 보기 어렵고, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>점자가 없으면 글을 읽기 힘들다.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>졸업식, 공개수업 등 학교 행사에 보호자가 참석하지 못해 위축된 적이…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>버스 등 대중교통을 이용할 때 다른 사람의 도움이…</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>없어도 문제없다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>없으면 어렵다</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3042,9 +3059,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3367,10 +3384,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="99">
@@ -3378,10 +3395,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="99">
@@ -3389,10 +3406,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="82.5">
@@ -3400,10 +3417,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="99">
@@ -3411,10 +3428,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="99">
@@ -3422,10 +3439,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="66">
@@ -3433,10 +3450,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="132">
@@ -3444,10 +3461,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="82.5">
@@ -3455,10 +3472,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="99">
@@ -3466,10 +3483,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="99">
@@ -3477,10 +3494,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="82.5">
@@ -3488,10 +3505,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="99">
@@ -3499,10 +3516,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="82.5">
@@ -3510,10 +3527,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="99">
@@ -3521,10 +3538,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="99">
@@ -3532,10 +3549,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="115.5">
@@ -3543,10 +3560,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="99">
@@ -3554,10 +3571,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="82.5">
@@ -3565,10 +3582,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="99">
@@ -3576,10 +3593,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="115.5">
@@ -3587,10 +3604,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="99">
@@ -3598,10 +3615,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="82.5">
@@ -3609,10 +3626,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="99">
@@ -3620,10 +3637,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="99">
@@ -3631,10 +3648,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="132">
@@ -3642,10 +3659,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="99">
@@ -3653,10 +3670,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="99">
@@ -3664,10 +3681,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="99">
@@ -3675,10 +3692,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="99">
@@ -3686,10 +3703,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3753,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -3756,7 +3773,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -3776,7 +3793,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -3796,7 +3813,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -3816,7 +3833,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -3836,7 +3853,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -3847,7 +3864,7 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>-1</v>
       </c>
     </row>
@@ -3856,7 +3873,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -3867,7 +3884,7 @@
       <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3876,18 +3893,18 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="7">
+        <v>17</v>
+      </c>
+      <c r="F9" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3896,18 +3913,18 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="7">
+        <v>20</v>
+      </c>
+      <c r="F10" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3916,19 +3933,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="5">
         <v>-1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3936,7 +3953,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -3947,7 +3964,7 @@
       <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3956,7 +3973,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -3967,7 +3984,7 @@
       <c r="E13" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>-1</v>
       </c>
     </row>
@@ -3976,18 +3993,18 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="7">
+        <v>25</v>
+      </c>
+      <c r="F14" s="5">
         <v>-1</v>
       </c>
     </row>
@@ -3996,18 +4013,18 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>-1</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="7">
+        <v>28</v>
+      </c>
+      <c r="F15" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4016,7 +4033,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -4027,7 +4044,7 @@
       <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4036,7 +4053,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -4047,7 +4064,7 @@
       <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4056,18 +4073,18 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="7">
+        <v>25</v>
+      </c>
+      <c r="F18" s="5">
         <v>-1</v>
       </c>
     </row>
@@ -4076,18 +4093,18 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="7">
+        <v>34</v>
+      </c>
+      <c r="F19" s="5">
         <v>-1</v>
       </c>
     </row>
@@ -4096,7 +4113,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
@@ -4107,7 +4124,7 @@
       <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4116,7 +4133,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
@@ -4127,13 +4144,14 @@
       <c r="E21" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4159,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="49.5">
@@ -4167,7 +4185,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -4183,16 +4201,16 @@
       <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
